--- a/mapping/SB_DWH/Mapping_FCT_RLOS_WORKSTEP_EVENT.xlsx
+++ b/mapping/SB_DWH/Mapping_FCT_RLOS_WORKSTEP_EVENT.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -167,8 +167,16 @@
     </font>
     <font>
       <name val="Times New Roman"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
-      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -239,7 +247,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -400,7 +408,10 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -707,15 +718,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
     <col width="19" customWidth="1" style="19" min="2" max="2"/>
     <col width="30.6640625" bestFit="1" customWidth="1" style="15" min="3" max="3"/>
-    <col width="36.6640625" bestFit="1" customWidth="1" style="16" min="4" max="4"/>
-    <col width="59.5" customWidth="1" style="19" min="5" max="5"/>
-    <col width="59.1640625" customWidth="1" style="16" min="6" max="6"/>
+    <col width="69.1640625" customWidth="1" style="16" min="4" max="4"/>
+    <col width="90.1640625" customWidth="1" style="19" min="5" max="5"/>
+    <col width="90.1640625" customWidth="1" style="16" min="6" max="6"/>
     <col width="9.1640625" customWidth="1" style="19" min="7" max="16384"/>
   </cols>
   <sheetData>
@@ -735,7 +746,6 @@
           <t>NG_SB_RLOS_ENTRY_EXIT AS A</t>
         </is>
       </c>
-      <c r="F1" s="52" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
@@ -753,7 +763,6 @@
           <t>DIM_RLOS_WORKSTEP_DECISION AS B</t>
         </is>
       </c>
-      <c r="F2" s="52" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="21" t="inlineStr">
@@ -771,7 +780,6 @@
           <t>DIM_LOS_USER AS C</t>
         </is>
       </c>
-      <c r="F3" s="52" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -789,7 +797,6 @@
           <t>DIM_RLOS_APPLICATION AS D</t>
         </is>
       </c>
-      <c r="F4" s="52" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="n"/>
@@ -798,7 +805,6 @@
           <t>WFINSTRUMENTTABLE AS G</t>
         </is>
       </c>
-      <c r="F5" s="52" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="n"/>
@@ -807,7 +813,6 @@
           <t>NG_SB_RLOS_USER_MAKE_WORK_STEP AS H</t>
         </is>
       </c>
-      <c r="F6" s="52" t="n"/>
     </row>
     <row r="7" hidden="1">
       <c r="A7" s="13" t="n"/>
@@ -816,42 +821,34 @@
           <t>NG_SB_RLOS_EXTTABLE AS I</t>
         </is>
       </c>
-      <c r="F7" s="52" t="n"/>
     </row>
     <row r="8" hidden="1">
       <c r="A8" s="13" t="n"/>
       <c r="E8" s="52" t="n"/>
-      <c r="F8" s="53" t="n"/>
     </row>
     <row r="9" hidden="1">
       <c r="A9" s="13" t="n"/>
       <c r="E9" s="53" t="n"/>
-      <c r="F9" s="52" t="n"/>
     </row>
     <row r="10" hidden="1">
       <c r="A10" s="13" t="n"/>
       <c r="E10" s="53" t="n"/>
-      <c r="F10" s="52" t="n"/>
     </row>
     <row r="11" hidden="1">
       <c r="A11" s="13" t="n"/>
       <c r="E11" s="53" t="n"/>
-      <c r="F11" s="52" t="n"/>
     </row>
     <row r="12" hidden="1">
       <c r="A12" s="13" t="n"/>
       <c r="E12" s="53" t="n"/>
-      <c r="F12" s="52" t="n"/>
     </row>
     <row r="13" hidden="1">
       <c r="A13" s="13" t="n"/>
       <c r="E13" s="53" t="n"/>
-      <c r="F13" s="52" t="n"/>
     </row>
     <row r="14" hidden="1">
       <c r="A14" s="13" t="n"/>
       <c r="E14" s="53" t="n"/>
-      <c r="F14" s="53" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
@@ -879,9 +876,8 @@
           <t>How to mapping RLOS</t>
         </is>
       </c>
-      <c r="F15" s="1" t="n"/>
-    </row>
-    <row r="16" ht="51" customHeight="1">
+    </row>
+    <row r="16">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -891,9 +887,8 @@
         </is>
       </c>
       <c r="E16" s="6" t="n"/>
-      <c r="F16" s="12" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
         <is>
           <t>DAYID</t>
@@ -909,19 +904,18 @@
           <t>Ngày dữ liệu</t>
         </is>
       </c>
-      <c r="D17" s="27" t="inlineStr">
+      <c r="D17" s="54" t="inlineStr">
         <is>
           <t>PK — Driving: NG_SB_RLOS_ENTRY_EXIT. Ngày dữ liệu, dạng số YYYYMMDD, TRUNC về 00:00:00. Là ngày phiên bản được ghi nhận, KHÔNG phải ảnh chụp lại toàn bộ nhật ký mỗi ngày — chỉ ghi bản ghi thay đổi/mới trong ngày TRUNC(REPLICAT_TIME) = v_batch_date</t>
         </is>
       </c>
-      <c r="E17" s="28" t="inlineStr">
+      <c r="E17" s="31" t="inlineStr">
         <is>
           <t>v_batch_date</t>
         </is>
       </c>
-      <c r="F17" s="28" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1">
+    </row>
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
           <t>WORKSTEP_EVENT_BK</t>
@@ -937,19 +931,18 @@
           <t>Khóa nghiệp vụ</t>
         </is>
       </c>
-      <c r="D18" s="27" t="inlineStr">
+      <c r="D18" s="54" t="inlineStr">
         <is>
           <t>Khóa nghiệp vụ của dòng sự kiện — gộp 3 cột PK tự nhiên cũ (WI_NAME, WORKSTEP_CODE, ENTRYDATE) thành 1 khóa đơn</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E18" s="31" t="inlineStr">
         <is>
           <t>STANDARD_HASH(A.WINAME || A.WORKSTEP || TO_CHAR(A.ENTRYDATE, 'YYYY-MM-DD HH24:MI:SS.FF6'), 'MD5')</t>
         </is>
       </c>
-      <c r="F18" s="28" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1">
+    </row>
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="28" t="inlineStr">
         <is>
           <t>WORKSTEP_DECISION_SK</t>
@@ -965,19 +958,18 @@
           <t>Khóa tới bước/quyết định</t>
         </is>
       </c>
-      <c r="D19" s="27" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_RLOS_WORKSTEP_DECISION (review 2026-09-24, gộp từ WORKSTEP_SK+DECISION_SK). KHÔNG nằm trong PK — chỉ để tra cứu thêm thuộc tính. Lookup theo cặp WORKSTEP_CODE (chính dòng event) + DECISION_CODE điều kiện thời gian [CẦN REVIEW] Mặc định -1 nếu không khớp</t>
-        </is>
-      </c>
-      <c r="E19" s="28" t="inlineStr">
+      <c r="D19" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_RLOS_WORKSTEP_DECISION. KHÔNG nằm trong PK — chỉ để tra cứu thêm thuộc tính. Lookup theo cặp WORKSTEP_CODE (chính dòng event) + DECISION_CODE điều kiện thời gian</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
         <is>
           <t>B.DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="F19" s="28" t="n"/>
-    </row>
-    <row r="20" ht="15" customFormat="1" customHeight="1" s="20">
+    </row>
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" s="28" t="inlineStr">
         <is>
           <t>USER_SK</t>
@@ -993,17 +985,16 @@
           <t>Khóa tới người xử lý</t>
         </is>
       </c>
-      <c r="D20" s="27" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_LOS_USER, người xử lý của chính sự kiện này. ĐÚNG GRAIN của bảng — 1 lần vào bước có đúng 1 người xử lý. KHÔNG nằm trong PK [CẦN REVIEW] Mặc định -1. USERNAME có thể rỗng khi bước chưa EXIT — vẫn map -1 bình thường</t>
-        </is>
-      </c>
-      <c r="E20" s="28" t="inlineStr">
+      <c r="D20" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_LOS_USER, người xử lý của chính sự kiện này. ĐÚNG GRAIN của bảng — 1 lần vào bước có đúng 1 người xử lý. KHÔNG nằm trong PK USERNAME có thể rỗng khi bước chưa EXIT — vẫn map -1 bình thường</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>C.DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="F20" s="28" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
@@ -1021,19 +1012,18 @@
           <t>Khóa tới hồ sơ tín dụng</t>
         </is>
       </c>
-      <c r="D21" s="27" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_RLOS_APPLICATION theo phiên bản hiệu lực tại DAYID [CẦN REVIEW] Mặc định -1</t>
-        </is>
-      </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="D21" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_RLOS_APPLICATION theo phiên bản hiệu lực tại DAYID</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>D.DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="F21" s="28" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1">
+    </row>
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
         <is>
           <t>WI_NAME</t>
@@ -1049,19 +1039,18 @@
           <t>Mã hồ sơ tín dụng</t>
         </is>
       </c>
-      <c r="D22" s="27" t="inlineStr">
+      <c r="D22" s="54" t="inlineStr">
         <is>
           <t>Mã hồ sơ tín dụng RLOS. Đổi tên WINAME→WI_NAME cho thống nhất với các bảng khác</t>
         </is>
       </c>
-      <c r="E22" s="28" t="inlineStr">
+      <c r="E22" s="31" t="inlineStr">
         <is>
           <t>A.WINAME</t>
         </is>
       </c>
-      <c r="F22" s="28" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1">
+    </row>
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="28" t="inlineStr">
         <is>
           <t>WORKSTEP_CODE</t>
@@ -1077,19 +1066,18 @@
           <t>Mã bước xử lý</t>
         </is>
       </c>
-      <c r="D23" s="27" t="inlineStr">
+      <c r="D23" s="54" t="inlineStr">
         <is>
           <t>Mã bước xử lý trên workflow. Đổi tên thêm hậu tố CODE, đã cắt tiền tố hệ nguồn nếu có</t>
         </is>
       </c>
-      <c r="E23" s="28" t="inlineStr">
+      <c r="E23" s="31" t="inlineStr">
         <is>
           <t>A.WORKSTEP</t>
         </is>
       </c>
-      <c r="F23" s="28" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1">
+    </row>
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
         <is>
           <t>ENTRYDATE</t>
@@ -1105,19 +1093,18 @@
           <t>Thời điểm vào bước</t>
         </is>
       </c>
-      <c r="D24" s="27" t="inlineStr">
+      <c r="D24" s="54" t="inlineStr">
         <is>
           <t>Thời điểm hồ sơ vào bước xử lý. Bắt buộc nằm trong khóa vì 1 hồ sơ có thể quay lại cùng 1 bước nhiều lần</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="E24" s="31" t="inlineStr">
         <is>
           <t>A.ENTRYDATE</t>
         </is>
       </c>
-      <c r="F24" s="28" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1">
+    </row>
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="28" t="inlineStr">
         <is>
           <t>EXITDATE</t>
@@ -1133,19 +1120,18 @@
           <t>Thời điểm ra khỏi bước</t>
         </is>
       </c>
-      <c r="D25" s="27" t="inlineStr">
+      <c r="D25" s="54" t="inlineStr">
         <is>
           <t>Thời điểm hồ sơ ra khỏi bước xử lý. NULL nghĩa là hồ sơ đang nằm tại bước này</t>
         </is>
       </c>
-      <c r="E25" s="28" t="inlineStr">
+      <c r="E25" s="31" t="inlineStr">
         <is>
           <t>A.EXITDATE</t>
         </is>
       </c>
-      <c r="F25" s="28" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1">
+    </row>
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
         <is>
           <t>USERNAME</t>
@@ -1161,17 +1147,16 @@
           <t>Tên tài khoản xử lý</t>
         </is>
       </c>
-      <c r="D26" s="27" t="inlineStr">
+      <c r="D26" s="54" t="inlineStr">
         <is>
           <t>Tên tài khoản người xử lý hồ sơ. Giữ nguyên giá trị gốc để báo cáo hiển thị thẳng, không phải join qua DIM_LOS_USER</t>
         </is>
       </c>
-      <c r="E26" s="28" t="inlineStr">
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>A.USERNAME</t>
         </is>
       </c>
-      <c r="F26" s="28" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
@@ -1189,19 +1174,18 @@
           <t>Ghi chú tại bước</t>
         </is>
       </c>
-      <c r="D27" s="27" t="inlineStr">
+      <c r="D27" s="54" t="inlineStr">
         <is>
           <t>Ghi chú tại bước xử lý</t>
         </is>
       </c>
-      <c r="E27" s="28" t="inlineStr">
+      <c r="E27" s="31" t="inlineStr">
         <is>
           <t>A.REMARKS</t>
         </is>
       </c>
-      <c r="F27" s="28" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1">
+    </row>
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="28" t="inlineStr">
         <is>
           <t>REASON_CODE</t>
@@ -1217,17 +1201,16 @@
           <t>Mã lý do hủy hồ sơ</t>
         </is>
       </c>
-      <c r="D28" s="27" t="inlineStr">
+      <c r="D28" s="54" t="inlineStr">
         <is>
           <t>Mã lý do hủy hồ sơ (chỉ RLOS có cột này). Bằng chứng cột-mức bổ sung cho việc tách vật lý CLOS/RLOS — CLOS không có cột tương ứng</t>
         </is>
       </c>
-      <c r="E28" s="28" t="inlineStr">
+      <c r="E28" s="31" t="inlineStr">
         <is>
           <t>A.REASON_CODE</t>
         </is>
       </c>
-      <c r="F28" s="28" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="28" t="inlineStr">
@@ -1245,19 +1228,18 @@
           <t>Diễn giải lý do hủy hồ sơ</t>
         </is>
       </c>
-      <c r="D29" s="27" t="inlineStr">
+      <c r="D29" s="54" t="inlineStr">
         <is>
           <t>Diễn giải lý do hủy hồ sơ (chỉ RLOS có cột này)</t>
         </is>
       </c>
-      <c r="E29" s="28" t="inlineStr">
+      <c r="E29" s="31" t="inlineStr">
         <is>
           <t>A.REASON_DESC</t>
         </is>
       </c>
-      <c r="F29" s="28" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
+    </row>
+    <row r="30" ht="45" customHeight="1">
       <c r="A30" s="28" t="inlineStr">
         <is>
           <t>TAT_SOURCE_SEC</t>
@@ -1273,19 +1255,18 @@
           <t>Thời gian xử lý (giây)</t>
         </is>
       </c>
-      <c r="D30" s="27" t="inlineStr">
-        <is>
-          <t>Thời gian xử lý do hệ nguồn ghi, đơn vị giây. Giữ lại để đối soát — 3 cột TAT_CALENDAR_HOUR/TAT_WORKING_HOUR/TAT_CPC_HOUR nay chuyển sang tính tại PDTD_DTM [CẦN REVIEW] Đơn vị 'giây' kế thừa từ extract gốc, cần DE xác nhận chính thức</t>
-        </is>
-      </c>
-      <c r="E30" s="28" t="inlineStr">
+      <c r="D30" s="54" t="inlineStr">
+        <is>
+          <t>Thời gian xử lý do hệ nguồn ghi, đơn vị giây. Giữ lại để đối soát — 3 cột TAT_CALENDAR_HOUR/TAT_WORKING_HOUR/TAT_CPC_HOUR nay chuyển sang tính tại PDTD_DTM</t>
+        </is>
+      </c>
+      <c r="E30" s="31" t="inlineStr">
         <is>
           <t>A.TAT</t>
         </is>
       </c>
-      <c r="F30" s="28" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
+    </row>
+    <row r="31" ht="75" customHeight="1">
       <c r="A31" s="28" t="inlineStr">
         <is>
           <t>PROCESSED_DATE</t>
@@ -1301,19 +1282,18 @@
           <t>Ngày xử lý hồ sơ</t>
         </is>
       </c>
-      <c r="D31" s="27" t="inlineStr">
+      <c r="D31" s="54" t="inlineStr">
         <is>
           <t>Ngày xử lý chung của hồ sơ theo 3 mức ưu tiên. PHÁI SINH TRỰC TIẾP trên bảng này, KHÔNG copy/JOIN từ FCT_RLOS_APPLICATION.PROCESSED_DATE. Phục vụ BC4.REPORT_DATE mà không cần JOIN fan-out sang APPLICATION_DAILY</t>
         </is>
       </c>
-      <c r="E31" s="28" t="inlineStr">
+      <c r="E31" s="31" t="inlineStr">
         <is>
           <t>COALESCE(MAX(CASE WHEN A.WORKSTEP IN ('CreditCommittee','CreditApproval') AND A.DECISION IN ('Send To HOSupport','Reject','Submit','Send To PostSanction','Submit To DisbursementMaker') THEN A.EXITDATE END) OVER (PARTITION BY A.WINAME), MAX(CASE WHEN A.WORKSTEP = 'UnderwriterMaker' AND A.DECISION = 'Cancel' THEN A.EXITDATE END) OVER (PARTITION BY A.WINAME), DAYID)</t>
         </is>
       </c>
-      <c r="F31" s="28" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1">
+    </row>
+    <row r="32" ht="75" customHeight="1">
       <c r="A32" s="28" t="inlineStr">
         <is>
           <t>WF_PROCESSNAME</t>
@@ -1329,19 +1309,18 @@
           <t>Tên hệ thống workflow</t>
         </is>
       </c>
-      <c r="D32" s="27" t="inlineStr">
+      <c r="D32" s="54" t="inlineStr">
         <is>
           <t>Tên hệ thống workflow của instance đang đứng — cột thô (thay cho WORKSTEP_FLAG đã tính sẵn). Lặp lại giống nhau trên mọi dòng event cùng WI_NAME. Nguồn cho chỉ tiêu WORKSTEP_FLAG (tính tại PDTD_DTM). JOIN không lọc điều kiện CREATEDBY — là business rule filter, chuyển xuống tính tại PDTD_DTM</t>
         </is>
       </c>
-      <c r="E32" s="28" t="inlineStr">
+      <c r="E32" s="31" t="inlineStr">
         <is>
           <t>G.PROCESSNAME</t>
         </is>
       </c>
-      <c r="F32" s="28" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1">
+    </row>
+    <row r="33" ht="45" customHeight="1">
       <c r="A33" s="28" t="inlineStr">
         <is>
           <t>WF_ACTIVITYNAME</t>
@@ -1357,19 +1336,18 @@
           <t>Bước hiện tại workflow</t>
         </is>
       </c>
-      <c r="D33" s="27" t="inlineStr">
+      <c r="D33" s="54" t="inlineStr">
         <is>
           <t>Bước hiện tại của instance workflow — cột thô. Cùng JOIN với WF_PROCESSNAME. Nguồn cho chỉ tiêu WORKSTEP_FLAG (tính tại PDTD_DTM), không lọc filter CREATEDBY</t>
         </is>
       </c>
-      <c r="E33" s="28" t="inlineStr">
+      <c r="E33" s="31" t="inlineStr">
         <is>
           <t>G.ACTIVITYNAME</t>
         </is>
       </c>
-      <c r="F33" s="28" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1">
+    </row>
+    <row r="34" ht="75" customHeight="1">
       <c r="A34" s="28" t="inlineStr">
         <is>
           <t>WF_CREATEDBY</t>
@@ -1385,19 +1363,18 @@
           <t>Người/hệ thống tạo bản ghi</t>
         </is>
       </c>
-      <c r="D34" s="27" t="inlineStr">
+      <c r="D34" s="54" t="inlineStr">
         <is>
           <t>Mã người/hệ thống tạo bản ghi workflow — cột thô, dùng để loại 5 tài khoản hệ thống/test khi tính WORKSTEP_FLAG tại PDTD_DTM. Bê nguyên giá trị thô từ nguồn — không áp điều kiện CREATEDBY NOT IN tại SB_DWH. Cùng JOIN với WF_PROCESSNAME/WF_ACTIVITYNAME</t>
         </is>
       </c>
-      <c r="E34" s="28" t="inlineStr">
+      <c r="E34" s="31" t="inlineStr">
         <is>
           <t>G.CREATEDBY</t>
         </is>
       </c>
-      <c r="F34" s="28" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1">
+    </row>
+    <row r="35" ht="165" customHeight="1">
       <c r="A35" s="28" t="inlineStr">
         <is>
           <t>UNDERWRITERMAKER_USERMAKE</t>
@@ -1413,19 +1390,18 @@
           <t>Người thẩm định (Maker)</t>
         </is>
       </c>
-      <c r="D35" s="27" t="inlineStr">
-        <is>
-          <t>CỘT MỚI (review 2026-10-15): chuyển từ FCT_RLOS_APPLICATION, input thô gắn với đúng 1 WORK_STEP cụ thể, phù hợp grain event-log hơn grain hồ sơ/ngày. Chỉ có giá trị khác NULL trên dòng event WORKSTEP_CODE='UnderwriterMaker'. JOIN điều kiện WORK_STEP = WORKSTEP_CODE của chính dòng event để không fan-out — dùng chung 1 JOIN duy nhất tới NG_SB_RLOS_USER_MAKE_WORK_STEP với UNDERWRITERCHECKER_USERMAKE/APPROVAL_USERMAKE, phân biệt bằng CASE WHEN theo WORKSTEP hiện tại của dòng. Bảng nguồn không có trong DS_BANG_202608.xlsx nhưng đã xác nhận tồn tại thật qua RLOS - Metadata.xlsx</t>
-        </is>
-      </c>
-      <c r="E35" s="28" t="inlineStr">
+      <c r="D35" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI: chuyển từ FCT_RLOS_APPLICATION, input thô gắn với đúng 1 WORK_STEP cụ thể, phù hợp grain event-log hơn grain hồ sơ/ngày. Chỉ có giá trị khác NULL trên dòng event WORKSTEP_CODE='UnderwriterMaker'. JOIN điều kiện WORK_STEP = WORKSTEP_CODE của chính dòng event để không fan-out — dùng chung 1 JOIN duy nhất tới NG_SB_RLOS_USER_MAKE_WORK_STEP với UNDERWRITERCHECKER_USERMAKE/APPROVAL_USERMAKE, phân biệt bằng CASE WHEN theo WORKSTEP hiện tại của dòng. Bảng nguồn không có trong DS_BANG_202608.xlsx nhưng đã xác nhận tồn tại thật qua RLOS - Metadata.xlsx</t>
+        </is>
+      </c>
+      <c r="E35" s="31" t="inlineStr">
         <is>
           <t>COALESCE(CASE WHEN A.WORKSTEP = 'UnderwriterMaker' THEN H.USER_MAKE END, I.UWMAKERUSER)</t>
         </is>
       </c>
-      <c r="F35" s="28" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1">
+    </row>
+    <row r="36" ht="75" customHeight="1">
       <c r="A36" s="28" t="inlineStr">
         <is>
           <t>UNDERWRITERCHECKER_USERMAKE</t>
@@ -1441,19 +1417,18 @@
           <t>Người thẩm định (Checker)</t>
         </is>
       </c>
-      <c r="D36" s="27" t="inlineStr">
-        <is>
-          <t>CỘT MỚI (review 2026-10-15): chuyển từ FCT_RLOS_APPLICATION, cùng cơ chế cột trên. Chỉ có giá trị khác NULL trên dòng event WORKSTEP_CODE='UnderwriterChecker'. Cùng JOIN duy nhất tới NG_SB_RLOS_USER_MAKE_WORK_STEP, phân biệt bằng CASE WHEN theo WORKSTEP hiện tại của dòng</t>
-        </is>
-      </c>
-      <c r="E36" s="28" t="inlineStr">
+      <c r="D36" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI: chuyển từ FCT_RLOS_APPLICATION, cùng cơ chế cột trên. Chỉ có giá trị khác NULL trên dòng event WORKSTEP_CODE='UnderwriterChecker'. Cùng JOIN duy nhất tới NG_SB_RLOS_USER_MAKE_WORK_STEP, phân biệt bằng CASE WHEN theo WORKSTEP hiện tại của dòng</t>
+        </is>
+      </c>
+      <c r="E36" s="31" t="inlineStr">
         <is>
           <t>COALESCE(CASE WHEN A.WORKSTEP = 'UnderwriterChecker' THEN H.USER_MAKE END, I.UWCHKRUSER)</t>
         </is>
       </c>
-      <c r="F36" s="28" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1">
+    </row>
+    <row r="37" ht="105" customHeight="1">
       <c r="A37" s="28" t="inlineStr">
         <is>
           <t>APPROVAL_USERMAKE</t>
@@ -1469,214 +1444,94 @@
           <t>Người phê duyệt</t>
         </is>
       </c>
-      <c r="D37" s="27" t="inlineStr">
-        <is>
-          <t>CỘT MỚI (review 2026-10-15): chuyển từ FCT_RLOS_APPLICATION. Chỉ có giá trị khác NULL trên dòng event WORKSTEP_CODE='CreditCommittee' hoặc 'CreditApproval'. Khác hẳn công thức CLOS (không hardcode theo APP_GRP, dùng 2 cột fallback CREDAPPRUSER/CCOMMITUSER trên chính NG_SB_RLOS_EXTTABLE). Cùng JOIN duy nhất tới NG_SB_RLOS_USER_MAKE_WORK_STEP với 2 cột USERMAKE trên, phân biệt bằng CASE WHEN theo WORKSTEP hiện tại của dòng</t>
-        </is>
-      </c>
-      <c r="E37" s="28" t="inlineStr">
+      <c r="D37" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI: chuyển từ FCT_RLOS_APPLICATION. Chỉ có giá trị khác NULL trên dòng event WORKSTEP_CODE='CreditCommittee' hoặc 'CreditApproval'. Khác hẳn công thức CLOS (không hardcode theo APP_GRP, dùng 2 cột fallback CREDAPPRUSER/CCOMMITUSER trên chính NG_SB_RLOS_EXTTABLE). Cùng JOIN duy nhất tới NG_SB_RLOS_USER_MAKE_WORK_STEP với 2 cột USERMAKE trên, phân biệt bằng CASE WHEN theo WORKSTEP hiện tại của dòng</t>
+        </is>
+      </c>
+      <c r="E37" s="31" t="inlineStr">
         <is>
           <t>COALESCE(CASE WHEN A.WORKSTEP IN ('CreditCommittee','CreditApproval') THEN H.USER_MAKE END, I.CREDAPPRUSER, I.CCOMMITUSER)</t>
         </is>
       </c>
-      <c r="F37" s="28" t="n"/>
-    </row>
-    <row r="38" ht="51" customHeight="1"/>
+    </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="10" t="n"/>
       <c r="B39" s="10" t="n"/>
       <c r="C39" s="10" t="n"/>
-      <c r="D39" s="54" t="inlineStr">
+      <c r="D39" s="55" t="inlineStr">
         <is>
           <t>Điều kiện join giữa các bảng</t>
         </is>
       </c>
       <c r="E39" s="10" t="n"/>
-      <c r="F39" s="10" t="n"/>
-    </row>
-    <row r="40" ht="60" customHeight="1">
+    </row>
+    <row r="40" ht="45" customHeight="1">
       <c r="A40" s="25" t="n"/>
       <c r="B40" s="25" t="n"/>
       <c r="C40" s="51" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="54" t="n"/>
       <c r="E40" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN B.WORKSTEP_CODE = A.WORKSTEP AND B.DECISION_CODE = A.DECISION AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
         </is>
       </c>
-      <c r="F40" s="8" t="n"/>
-    </row>
-    <row r="41" ht="45" customHeight="1">
+    </row>
+    <row r="41" ht="30" customHeight="1">
       <c r="A41" s="25" t="n"/>
       <c r="B41" s="25" t="n"/>
       <c r="C41" s="51" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="54" t="n"/>
       <c r="E41" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN C.USERNAME = A.USERNAME AND v_batch_date BETWEEN C.EFF_DATE AND NVL(C.EXP_DATE, v_batch_date)</t>
         </is>
       </c>
-      <c r="F41" s="8" t="n"/>
-    </row>
-    <row r="42" ht="45" customHeight="1">
+    </row>
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" s="25" t="n"/>
       <c r="B42" s="25" t="n"/>
       <c r="C42" s="51" t="n"/>
-      <c r="D42" s="8" t="n"/>
+      <c r="D42" s="54" t="n"/>
       <c r="E42" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN D.WI_NAME = A.WINAME AND v_batch_date BETWEEN D.EFF_DATE AND NVL(D.EXP_DATE, v_batch_date)</t>
         </is>
       </c>
-      <c r="F42" s="8" t="n"/>
-    </row>
-    <row r="43" ht="60" customHeight="1">
+    </row>
+    <row r="43" ht="30" customHeight="1">
       <c r="A43" s="25" t="n"/>
       <c r="B43" s="25" t="n"/>
       <c r="C43" s="51" t="n"/>
-      <c r="D43" s="8" t="n"/>
+      <c r="D43" s="54" t="n"/>
       <c r="E43" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN G.PROCESSINSTANCEID = A.WINAME AND ROW_NUMBER() OVER (PARTITION BY G.PROCESSINSTANCEID ORDER BY G.CREATEDBY) = 1</t>
         </is>
       </c>
-      <c r="F43" s="8" t="n"/>
-    </row>
-    <row r="44" ht="30" customHeight="1">
+    </row>
+    <row r="44" ht="15" customHeight="1">
       <c r="A44" s="25" t="n"/>
       <c r="B44" s="25" t="n"/>
       <c r="C44" s="51" t="n"/>
-      <c r="D44" s="8" t="n"/>
+      <c r="D44" s="54" t="n"/>
       <c r="E44" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN H.WI_NAME = A.WINAME AND H.WORK_STEP = A.WORKSTEP</t>
         </is>
       </c>
-      <c r="F44" s="8" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="25" t="n"/>
       <c r="B45" s="25" t="n"/>
       <c r="C45" s="51" t="n"/>
-      <c r="D45" s="8" t="n"/>
+      <c r="D45" s="54" t="n"/>
       <c r="E45" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN I.WI_NAME = A.WINAME</t>
         </is>
       </c>
-      <c r="F45" s="8" t="n"/>
-    </row>
-    <row r="46" ht="34" customHeight="1"/>
-    <row r="47" ht="17" customHeight="1"/>
-    <row r="48" ht="17" customHeight="1"/>
-    <row r="49" ht="17" customHeight="1"/>
-    <row r="50" ht="51" customHeight="1"/>
-    <row r="51" ht="51" customHeight="1"/>
-    <row r="52" ht="34" customHeight="1"/>
-    <row r="53" ht="34" customHeight="1"/>
-    <row r="54" ht="34" customHeight="1"/>
-    <row r="55" ht="34" customHeight="1"/>
-    <row r="56" ht="68" customHeight="1"/>
-    <row r="57" ht="51" customHeight="1"/>
-    <row r="58" ht="34" customHeight="1"/>
-    <row r="59" ht="17" customHeight="1"/>
-    <row r="60" ht="34" customHeight="1"/>
-    <row r="61" ht="17" customHeight="1"/>
-    <row r="62" ht="85" customHeight="1"/>
-    <row r="63" ht="85" customHeight="1"/>
-    <row r="64" ht="34" customHeight="1"/>
-    <row r="65" ht="17" customHeight="1"/>
-    <row r="66" ht="34" customHeight="1"/>
-    <row r="67" ht="51" customHeight="1"/>
-    <row r="68" ht="51" customHeight="1"/>
-    <row r="69" ht="51" customHeight="1"/>
-    <row r="70" ht="17" customHeight="1"/>
-    <row r="71" ht="34" customHeight="1"/>
-    <row r="72" ht="34" customHeight="1"/>
-    <row r="73" ht="34" customHeight="1"/>
-    <row r="74" ht="34" customHeight="1"/>
-    <row r="75" ht="34" customHeight="1"/>
-    <row r="76" ht="34" customHeight="1"/>
-    <row r="77" ht="51" customHeight="1"/>
-    <row r="78" ht="34" customHeight="1"/>
-    <row r="79" ht="51" customHeight="1"/>
-    <row r="80" ht="17" customHeight="1"/>
-    <row r="81" ht="17" customHeight="1"/>
-    <row r="82" ht="17" customHeight="1"/>
-    <row r="83" ht="17" customHeight="1"/>
-    <row r="84" ht="17" customHeight="1"/>
-    <row r="85" ht="17" customHeight="1"/>
-    <row r="86" ht="17" customHeight="1"/>
-    <row r="87" ht="17" customHeight="1"/>
-    <row r="88" ht="17" customHeight="1"/>
-    <row r="89" ht="17" customHeight="1"/>
-    <row r="90" ht="34" customHeight="1"/>
-    <row r="91" ht="17" customHeight="1"/>
-    <row r="92" ht="17" customHeight="1"/>
-    <row r="93" ht="17" customHeight="1"/>
-    <row r="94" ht="17" customHeight="1"/>
-    <row r="95" ht="17" customHeight="1"/>
-    <row r="96" ht="17" customHeight="1"/>
-    <row r="97" ht="17" customHeight="1"/>
-    <row r="100" ht="187" customHeight="1"/>
-    <row r="101" ht="17" customHeight="1"/>
-    <row r="102" ht="17" customHeight="1"/>
-    <row r="103" ht="17" customHeight="1"/>
-    <row r="104" ht="17" customHeight="1"/>
-    <row r="105" ht="17" customHeight="1"/>
-    <row r="106" ht="17" customHeight="1"/>
-    <row r="107" ht="17" customHeight="1"/>
-    <row r="108" ht="17" customHeight="1"/>
-    <row r="109" ht="17" customHeight="1"/>
-    <row r="110" ht="17" customHeight="1"/>
-    <row r="111" ht="17" customHeight="1"/>
-    <row r="112" ht="17" customHeight="1"/>
-    <row r="113" ht="17" customHeight="1"/>
-    <row r="114" ht="17" customHeight="1"/>
-    <row r="115" ht="17" customHeight="1"/>
-    <row r="116" ht="17" customHeight="1"/>
-    <row r="117" ht="17" customHeight="1"/>
-    <row r="118" ht="17" customHeight="1"/>
-    <row r="119" ht="17" customHeight="1"/>
-    <row r="120" ht="68" customHeight="1"/>
-    <row r="121" ht="51" customHeight="1"/>
-    <row r="122" ht="34" customHeight="1"/>
-    <row r="123" ht="153" customHeight="1"/>
-    <row r="124" ht="17" customHeight="1"/>
-    <row r="125" ht="17" customHeight="1"/>
-    <row r="132" ht="60" customHeight="1"/>
-    <row r="133" ht="17" customHeight="1"/>
-    <row r="134" ht="17" customHeight="1"/>
-    <row r="135" ht="17" customHeight="1"/>
-    <row r="136" ht="17" customHeight="1"/>
-    <row r="137" ht="51" customHeight="1"/>
-    <row r="138" ht="45" customHeight="1"/>
-    <row r="139" ht="120" customHeight="1"/>
-    <row r="141" ht="384" customHeight="1"/>
-    <row r="143" ht="34" customHeight="1"/>
-    <row r="148" ht="119" customHeight="1"/>
-    <row r="149" ht="17" customHeight="1"/>
-    <row r="150" ht="17" customHeight="1"/>
-    <row r="151" ht="17" customHeight="1"/>
-    <row r="152" ht="51" customHeight="1"/>
-    <row r="153" ht="34" customHeight="1"/>
-    <row r="154" ht="30" customHeight="1"/>
-    <row r="155" ht="17" customHeight="1"/>
-    <row r="157" ht="119" customHeight="1"/>
-    <row r="158" ht="17" customHeight="1"/>
-    <row r="159" ht="17" customHeight="1"/>
-    <row r="160" ht="17" customHeight="1"/>
-    <row r="161" ht="17" customHeight="1"/>
-    <row r="162" ht="17" customHeight="1"/>
-    <row r="163" ht="17" customHeight="1"/>
-    <row r="164" ht="17" customHeight="1"/>
-    <row r="165" ht="17" customHeight="1"/>
-    <row r="166" ht="34" customHeight="1"/>
-    <row r="167" ht="34" customHeight="1"/>
-    <row r="168" ht="16" customHeight="1"/>
-    <row r="169" ht="17" customHeight="1"/>
-    <row r="170" ht="17" customHeight="1"/>
-    <row r="2480" customFormat="1" s="19"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/mapping/SB_DWH/Mapping_FCT_RLOS_WORKSTEP_EVENT.xlsx
+++ b/mapping/SB_DWH/Mapping_FCT_RLOS_WORKSTEP_EVENT.xlsx
@@ -718,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>Bảng Fact nhật ký sự kiện xử lý hồ sơ RLOS, driving từ NG_SB_RLOS_ENTRY_EXIT</t>
+          <t>Bảng FACT nhật ký workflow mức nguyên tử của hệ RLOS (bán lẻ/cá nhân) — mỗi dòng là 1 lần hồ sơ đi qua 1 bước xử lý (workstep) trên workflow</t>
         </is>
       </c>
       <c r="E2" s="52" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="E3" s="52" t="inlineStr">
         <is>
-          <t>DIM_LOS_USER AS C</t>
+          <t>DIM_RLOS_APPLICATION AS C</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="E4" s="52" t="inlineStr">
         <is>
-          <t>DIM_RLOS_APPLICATION AS D</t>
+          <t>DIM_LOS_USER AS D</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       <c r="A5" s="13" t="n"/>
       <c r="E5" s="52" t="inlineStr">
         <is>
-          <t>WFINSTRUMENTTABLE AS G</t>
+          <t>WFINSTRUMENTTABLE AS E</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       <c r="A6" s="13" t="n"/>
       <c r="E6" s="52" t="inlineStr">
         <is>
-          <t>NG_SB_RLOS_USER_MAKE_WORK_STEP AS H</t>
+          <t>NG_SB_RLOS_USER_MAKE_WORK_STEP AS F</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       <c r="A7" s="13" t="n"/>
       <c r="E7" s="52" t="inlineStr">
         <is>
-          <t>NG_SB_RLOS_EXTTABLE AS I</t>
+          <t>NG_SB_RLOS_EXTTABLE AS G</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="D17" s="54" t="inlineStr">
         <is>
-          <t>PK — Driving: NG_SB_RLOS_ENTRY_EXIT. Ngày dữ liệu, dạng số YYYYMMDD, TRUNC về 00:00:00. Là ngày phiên bản được ghi nhận, KHÔNG phải ảnh chụp lại toàn bộ nhật ký mỗi ngày — chỉ ghi bản ghi thay đổi/mới trong ngày TRUNC(REPLICAT_TIME) = v_batch_date</t>
+          <t>Ngày dữ liệu, dạng số YYYYMMDD, TRUNC về 00:00:00. Là ngày phiên bản được ghi nhận, KHÔNG phải ảnh chụp lại toàn bộ nhật ký mỗi ngày — chỉ ghi bản ghi thay đổi/mới trong TRUNC(REPLICAT_TIME) = v_batch_date.</t>
         </is>
       </c>
       <c r="E17" s="31" t="inlineStr">
@@ -915,7 +915,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
+    <row r="18" ht="90" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
           <t>WORKSTEP_EVENT_BK</t>
@@ -928,12 +928,12 @@
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>Khóa nghiệp vụ</t>
+          <t>Khóa nghiệp vụ sự kiện</t>
         </is>
       </c>
       <c r="D18" s="54" t="inlineStr">
         <is>
-          <t>Khóa nghiệp vụ của dòng sự kiện — gộp 3 cột PK tự nhiên cũ (WI_NAME, WORKSTEP_CODE, ENTRYDATE) thành 1 khóa đơn</t>
+          <t>Khóa nghiệp vụ của dòng sự kiện — gộp 3 cột PK tự nhiên cũ (WI_NAME, WORKSTEP_CODE, ENTRYDATE) thành 1 khóa đơn. PK đổi từ composite (DAYID,WI_NAME,WORKSTEP_CODE,ENTRYDATE) thành (DAYID,WORKSTEP_EVENT_BK). Không có thành phần DATASOURCE trong công thức hash.</t>
         </is>
       </c>
       <c r="E18" s="31" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="45" customHeight="1">
+    <row r="19" ht="75" customHeight="1">
       <c r="A19" s="28" t="inlineStr">
         <is>
           <t>WORKSTEP_DECISION_SK</t>
@@ -955,12 +955,12 @@
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới bước/quyết định</t>
+          <t>Khóa bước &amp; quyết định</t>
         </is>
       </c>
       <c r="D19" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_RLOS_WORKSTEP_DECISION. KHÔNG nằm trong PK — chỉ để tra cứu thêm thuộc tính. Lookup theo cặp WORKSTEP_CODE (chính dòng event) + DECISION_CODE điều kiện thời gian</t>
+          <t>Khóa tới DIM_RLOS_WORKSTEP_DECISION. KHÔNG nằm trong PK — chỉ để tra cứu thêm thuộc tính (kể cả DECISION_CODE, đã xóa denormalize khỏi fact). Lookup theo cặp WORKSTEP_CODE (chính dòng event) + DECISION_CODE điều kiện thời gian. Mặc định -1 nếu không khớp</t>
         </is>
       </c>
       <c r="E19" s="31" t="inlineStr">
@@ -969,522 +969,538 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
+    <row r="20" ht="90" customHeight="1">
       <c r="A20" s="28" t="inlineStr">
         <is>
-          <t>USER_SK</t>
+          <t>WORKSTEP_CODE</t>
         </is>
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(200)</t>
         </is>
       </c>
       <c r="C20" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới người xử lý</t>
+          <t>Mã bước xử lý</t>
         </is>
       </c>
       <c r="D20" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_LOS_USER, người xử lý của chính sự kiện này. ĐÚNG GRAIN của bảng — 1 lần vào bước có đúng 1 người xử lý. KHÔNG nằm trong PK USERNAME có thể rỗng khi bước chưa EXIT — vẫn map -1 bình thường</t>
+          <t>Mã bước xử lý trên workflow — vị trí liền sau WORKSTEP_DECISION_SK: BK composite (cùng DECISION_CODE), đồng thời là 1 phần cấu thành WORKSTEP_EVENT_BK. Đổi tên thêm hậu tố CODE, đã cắt tiền tố hệ nguồn nếu có. Không còn là thành phần PK riêng lẻ — PK đã gộp vào WORKSTEP_EVENT_BK (DAYID+WORKSTEP_EVENT_BK).</t>
         </is>
       </c>
       <c r="E20" s="31" t="inlineStr">
         <is>
-          <t>C.DIMENSION_KEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
+          <t>A.WORKSTEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
-          <t>APPLICATION_SK</t>
+          <t>DECISION_CODE</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(200)</t>
         </is>
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới hồ sơ tín dụng</t>
+          <t>Mã quyết định bước</t>
         </is>
       </c>
       <c r="D21" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_RLOS_APPLICATION theo phiên bản hiệu lực tại DAYID</t>
+          <t>CỘT MỚI — BK cạnh SK: nửa còn lại của BK composite DIM_RLOS_WORKSTEP_DECISION (WORKSTEP_CODE đã có sẵn ở cột liền trước)</t>
         </is>
       </c>
       <c r="E21" s="31" t="inlineStr">
         <is>
-          <t>D.DIMENSION_KEY</t>
+          <t>A.DECISION</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
         <is>
+          <t>APPLICATION_SK</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Khóa hồ sơ tín dụng</t>
+        </is>
+      </c>
+      <c r="D22" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_RLOS_APPLICATION theo phiên bản hiệu lực tại DAYID. Mặc định -1</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>C.DIMENSION_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="75" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
           <t>WI_NAME</t>
         </is>
       </c>
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C23" s="26" t="inlineStr">
         <is>
           <t>Mã hồ sơ tín dụng</t>
         </is>
       </c>
-      <c r="D22" s="54" t="inlineStr">
-        <is>
-          <t>Mã hồ sơ tín dụng RLOS. Đổi tên WINAME→WI_NAME cho thống nhất với các bảng khác</t>
-        </is>
-      </c>
-      <c r="E22" s="31" t="inlineStr">
+      <c r="D23" s="54" t="inlineStr">
+        <is>
+          <t>Mã hồ sơ tín dụng RLOS — vị trí liền sau APPLICATION_SK: BK của APPLICATION_SK, đồng thời là 1 phần cấu thành WORKSTEP_EVENT_BK. Đổi tên WINAME→WI_NAME cho thống nhất với các bảng khác. Không còn là thành phần PK riêng lẻ — PK đã gộp vào WORKSTEP_EVENT_BK (DAYID+WORKSTEP_EVENT_BK).</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
         <is>
           <t>A.WINAME</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>WORKSTEP_CODE</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(200)</t>
-        </is>
-      </c>
-      <c r="C23" s="26" t="inlineStr">
-        <is>
-          <t>Mã bước xử lý</t>
-        </is>
-      </c>
-      <c r="D23" s="54" t="inlineStr">
-        <is>
-          <t>Mã bước xử lý trên workflow. Đổi tên thêm hậu tố CODE, đã cắt tiền tố hệ nguồn nếu có</t>
-        </is>
-      </c>
-      <c r="E23" s="31" t="inlineStr">
-        <is>
-          <t>A.WORKSTEP</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
         <is>
+          <t>USER_SK</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Khóa người xử lý</t>
+        </is>
+      </c>
+      <c r="D24" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_LOS_USER, người xử lý của chính sự kiện này. ĐÚNG GRAIN của bảng — 1 lần vào bước có đúng 1 người xử lý. KHÔNG nằm trong PK. Mặc định -1. USERNAME có thể rỗng khi bước chưa EXIT — vẫn map -1 bình thường</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>D.DIMENSION_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
           <t>ENTRYDATE</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>TIMESTAMP</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C25" s="26" t="inlineStr">
         <is>
           <t>Thời điểm vào bước</t>
         </is>
       </c>
-      <c r="D24" s="54" t="inlineStr">
-        <is>
-          <t>Thời điểm hồ sơ vào bước xử lý. Bắt buộc nằm trong khóa vì 1 hồ sơ có thể quay lại cùng 1 bước nhiều lần</t>
-        </is>
-      </c>
-      <c r="E24" s="31" t="inlineStr">
+      <c r="D25" s="54" t="inlineStr">
+        <is>
+          <t>Thời điểm hồ sơ vào bước xử lý. Bắt buộc nằm trong khóa vì 1 hồ sơ có thể quay lại cùng 1 bước nhiều lần. Không còn là thành phần PK riêng lẻ — PK đã gộp vào WORKSTEP_EVENT_BK (DAYID+WORKSTEP_EVENT_BK).</t>
+        </is>
+      </c>
+      <c r="E25" s="31" t="inlineStr">
         <is>
           <t>A.ENTRYDATE</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>EXITDATE</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>Thời điểm ra khỏi bước</t>
-        </is>
-      </c>
-      <c r="D25" s="54" t="inlineStr">
-        <is>
-          <t>Thời điểm hồ sơ ra khỏi bước xử lý. NULL nghĩa là hồ sơ đang nằm tại bước này</t>
-        </is>
-      </c>
-      <c r="E25" s="31" t="inlineStr">
-        <is>
-          <t>A.EXITDATE</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
         <is>
+          <t>EXITDATE</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Thời điểm ra bước</t>
+        </is>
+      </c>
+      <c r="D26" s="54" t="inlineStr">
+        <is>
+          <t>Thời điểm hồ sơ ra khỏi bước xử lý. NULL nghĩa là hồ sơ đang nằm tại bước này</t>
+        </is>
+      </c>
+      <c r="E26" s="31" t="inlineStr">
+        <is>
+          <t>A.EXITDATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
           <t>USERNAME</t>
         </is>
       </c>
-      <c r="B26" s="25" t="inlineStr">
+      <c r="B27" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr">
+      <c r="C27" s="26" t="inlineStr">
         <is>
           <t>Tên tài khoản xử lý</t>
         </is>
       </c>
-      <c r="D26" s="54" t="inlineStr">
+      <c r="D27" s="54" t="inlineStr">
         <is>
           <t>Tên tài khoản người xử lý hồ sơ. Giữ nguyên giá trị gốc để báo cáo hiển thị thẳng, không phải join qua DIM_LOS_USER</t>
         </is>
       </c>
-      <c r="E26" s="31" t="inlineStr">
+      <c r="E27" s="31" t="inlineStr">
         <is>
           <t>A.USERNAME</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="28" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="28" t="inlineStr">
         <is>
           <t>REMARKS</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(4000)</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
-        <is>
-          <t>Ghi chú tại bước</t>
-        </is>
-      </c>
-      <c r="D27" s="54" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>Ghi chú bước xử lý</t>
+        </is>
+      </c>
+      <c r="D28" s="54" t="inlineStr">
         <is>
           <t>Ghi chú tại bước xử lý</t>
         </is>
       </c>
-      <c r="E27" s="31" t="inlineStr">
+      <c r="E28" s="31" t="inlineStr">
         <is>
           <t>A.REMARKS</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="28" t="inlineStr">
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>REASON_CODE</t>
         </is>
       </c>
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B29" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>Mã lý do hủy hồ sơ</t>
         </is>
       </c>
-      <c r="D28" s="54" t="inlineStr">
+      <c r="D29" s="54" t="inlineStr">
         <is>
           <t>Mã lý do hủy hồ sơ (chỉ RLOS có cột này). Bằng chứng cột-mức bổ sung cho việc tách vật lý CLOS/RLOS — CLOS không có cột tương ứng</t>
         </is>
       </c>
-      <c r="E28" s="31" t="inlineStr">
+      <c r="E29" s="31" t="inlineStr">
         <is>
           <t>A.REASON_CODE</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="28" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>REASON_DESC</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B30" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(500)</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
-        <is>
-          <t>Diễn giải lý do hủy hồ sơ</t>
-        </is>
-      </c>
-      <c r="D29" s="54" t="inlineStr">
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>Diễn giải lý do hủy</t>
+        </is>
+      </c>
+      <c r="D30" s="54" t="inlineStr">
         <is>
           <t>Diễn giải lý do hủy hồ sơ (chỉ RLOS có cột này)</t>
         </is>
       </c>
-      <c r="E29" s="31" t="inlineStr">
+      <c r="E30" s="31" t="inlineStr">
         <is>
           <t>A.REASON_DESC</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="45" customHeight="1">
-      <c r="A30" s="28" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="28" t="inlineStr">
         <is>
           <t>TAT_SOURCE_SEC</t>
         </is>
       </c>
-      <c r="B30" s="25" t="inlineStr">
+      <c r="B31" s="25" t="inlineStr">
         <is>
           <t>NUMBER(12)</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
-        <is>
-          <t>Thời gian xử lý (giây)</t>
-        </is>
-      </c>
-      <c r="D30" s="54" t="inlineStr">
-        <is>
-          <t>Thời gian xử lý do hệ nguồn ghi, đơn vị giây. Giữ lại để đối soát — 3 cột TAT_CALENDAR_HOUR/TAT_WORKING_HOUR/TAT_CPC_HOUR nay chuyển sang tính tại PDTD_DTM</t>
-        </is>
-      </c>
-      <c r="E30" s="31" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>TAT nguồn (giây)</t>
+        </is>
+      </c>
+      <c r="D31" s="54" t="inlineStr">
+        <is>
+          <t>Thời gian xử lý do hệ nguồn ghi, đơn vị giây. Giữ lại để đối soát — 3 cột TAT_CALENDAR_HOUR/TAT_WORKING_HOUR/TAT_CPC_HOUR nay chuyển sang tính tại PDTD_DTM. Đơn vị 'giây' kế thừa từ extract gốc, cần DE xác nhận chính thức</t>
+        </is>
+      </c>
+      <c r="E31" s="31" t="inlineStr">
         <is>
           <t>A.TAT</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="75" customHeight="1">
-      <c r="A31" s="28" t="inlineStr">
+    <row r="32" ht="150" customHeight="1">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>PROCESSED_DATE</t>
         </is>
       </c>
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B32" s="25" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C31" s="26" t="inlineStr">
+      <c r="C32" s="26" t="inlineStr">
         <is>
           <t>Ngày xử lý hồ sơ</t>
         </is>
       </c>
-      <c r="D31" s="54" t="inlineStr">
-        <is>
-          <t>Ngày xử lý chung của hồ sơ theo 3 mức ưu tiên. PHÁI SINH TRỰC TIẾP trên bảng này, KHÔNG copy/JOIN từ FCT_RLOS_APPLICATION.PROCESSED_DATE. Phục vụ BC4.REPORT_DATE mà không cần JOIN fan-out sang APPLICATION_DAILY</t>
-        </is>
-      </c>
-      <c r="E31" s="31" t="inlineStr">
+      <c r="D32" s="54" t="inlineStr">
+        <is>
+          <t>Ngày xử lý chung của hồ sơ theo 3 mức ưu tiên. PHÁI SINH TRỰC TIẾP trên bảng này, KHÔNG copy/JOIN từ FCT_RLOS_APPLICATION.PROCESSED_DATE. COALESCE theo 3 mức ưu tiên (window function trên chính driving table): (1) MAX(EXITDATE) tại bước phê duyệt đã hoàn tất; (2) EXITDATE tại WORKSTEP='UnderwriterMaker' AND DECISION='Cancel'; (3) DAYID. Cùng công thức/kết quả với FCT_RLOS_APPLICATION.PROCESSED_DATE cho cùng WI_NAME. Phục vụ BC4.REPORT_DATE mà không cần JOIN fan-out sang APPLICATION_DAILY</t>
+        </is>
+      </c>
+      <c r="E32" s="31" t="inlineStr">
         <is>
           <t>COALESCE(MAX(CASE WHEN A.WORKSTEP IN ('CreditCommittee','CreditApproval') AND A.DECISION IN ('Send To HOSupport','Reject','Submit','Send To PostSanction','Submit To DisbursementMaker') THEN A.EXITDATE END) OVER (PARTITION BY A.WINAME), MAX(CASE WHEN A.WORKSTEP = 'UnderwriterMaker' AND A.DECISION = 'Cancel' THEN A.EXITDATE END) OVER (PARTITION BY A.WINAME), DAYID)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="75" customHeight="1">
-      <c r="A32" s="28" t="inlineStr">
+    <row r="33" ht="120" customHeight="1">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>WF_PROCESSNAME</t>
         </is>
       </c>
-      <c r="B32" s="25" t="inlineStr">
+      <c r="B33" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
         <is>
           <t>Tên hệ thống workflow</t>
         </is>
       </c>
-      <c r="D32" s="54" t="inlineStr">
-        <is>
-          <t>Tên hệ thống workflow của instance đang đứng — cột thô (thay cho WORKSTEP_FLAG đã tính sẵn). Lặp lại giống nhau trên mọi dòng event cùng WI_NAME. Nguồn cho chỉ tiêu WORKSTEP_FLAG (tính tại PDTD_DTM). JOIN không lọc điều kiện CREATEDBY — là business rule filter, chuyển xuống tính tại PDTD_DTM</t>
-        </is>
-      </c>
-      <c r="E32" s="31" t="inlineStr">
-        <is>
-          <t>G.PROCESSNAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="45" customHeight="1">
-      <c r="A33" s="28" t="inlineStr">
+      <c r="D33" s="54" t="inlineStr">
+        <is>
+          <t>Tên hệ thống workflow của instance đang đứng — cột thô (thay cho WORKSTEP_FLAG đã tính sẵn). Lặp lại giống nhau trên mọi dòng event cùng WI_NAME. Nguồn cho chỉ tiêu WORKSTEP_FLAG (tính tại PDTD_DTM). JOIN không lọc điều kiện CREATEDBY (NOT IN 5 tài khoản hệ thống/test) — đây là business rule filter, không phải điều kiện khóa join, nên chuyển xuống tính tại PDTD_DTM ngay trước khi dùng để tính WORKSTEP_FLAG, cùng nguyên tắc SB_DWH chỉ ảnh chụp sạch nguồn.</t>
+        </is>
+      </c>
+      <c r="E33" s="31" t="inlineStr">
+        <is>
+          <t>E.PROCESSNAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t>WF_ACTIVITYNAME</t>
         </is>
       </c>
-      <c r="B33" s="25" t="inlineStr">
+      <c r="B34" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C33" s="26" t="inlineStr">
+      <c r="C34" s="26" t="inlineStr">
         <is>
           <t>Bước hiện tại workflow</t>
         </is>
       </c>
-      <c r="D33" s="54" t="inlineStr">
-        <is>
-          <t>Bước hiện tại của instance workflow — cột thô. Cùng JOIN với WF_PROCESSNAME. Nguồn cho chỉ tiêu WORKSTEP_FLAG (tính tại PDTD_DTM), không lọc filter CREATEDBY</t>
-        </is>
-      </c>
-      <c r="E33" s="31" t="inlineStr">
-        <is>
-          <t>G.ACTIVITYNAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="75" customHeight="1">
-      <c r="A34" s="28" t="inlineStr">
+      <c r="D34" s="54" t="inlineStr">
+        <is>
+          <t>Bước hiện tại của instance workflow — cột thô. Cùng JOIN với WF_PROCESSNAME. Nguồn cho chỉ tiêu WORKSTEP_FLAG (tính tại PDTD_DTM), không lọc filter CREATEDBY trong JOIN này (cùng lý do WF_PROCESSNAME).</t>
+        </is>
+      </c>
+      <c r="E34" s="31" t="inlineStr">
+        <is>
+          <t>E.ACTIVITYNAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="120" customHeight="1">
+      <c r="A35" s="28" t="inlineStr">
         <is>
           <t>WF_CREATEDBY</t>
         </is>
       </c>
-      <c r="B34" s="25" t="inlineStr">
+      <c r="B35" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C34" s="26" t="inlineStr">
-        <is>
-          <t>Người/hệ thống tạo bản ghi</t>
-        </is>
-      </c>
-      <c r="D34" s="54" t="inlineStr">
-        <is>
-          <t>Mã người/hệ thống tạo bản ghi workflow — cột thô, dùng để loại 5 tài khoản hệ thống/test khi tính WORKSTEP_FLAG tại PDTD_DTM. Bê nguyên giá trị thô từ nguồn — không áp điều kiện CREATEDBY NOT IN tại SB_DWH. Cùng JOIN với WF_PROCESSNAME/WF_ACTIVITYNAME</t>
-        </is>
-      </c>
-      <c r="E34" s="31" t="inlineStr">
-        <is>
-          <t>G.CREATEDBY</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="165" customHeight="1">
-      <c r="A35" s="28" t="inlineStr">
-        <is>
-          <t>UNDERWRITERMAKER_USERMAKE</t>
-        </is>
-      </c>
-      <c r="B35" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
       <c r="C35" s="26" t="inlineStr">
         <is>
-          <t>Người thẩm định (Maker)</t>
+          <t>Người tạo bản ghi workflow</t>
         </is>
       </c>
       <c r="D35" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI: chuyển từ FCT_RLOS_APPLICATION, input thô gắn với đúng 1 WORK_STEP cụ thể, phù hợp grain event-log hơn grain hồ sơ/ngày. Chỉ có giá trị khác NULL trên dòng event WORKSTEP_CODE='UnderwriterMaker'. JOIN điều kiện WORK_STEP = WORKSTEP_CODE của chính dòng event để không fan-out — dùng chung 1 JOIN duy nhất tới NG_SB_RLOS_USER_MAKE_WORK_STEP với UNDERWRITERCHECKER_USERMAKE/APPROVAL_USERMAKE, phân biệt bằng CASE WHEN theo WORKSTEP hiện tại của dòng. Bảng nguồn không có trong DS_BANG_202608.xlsx nhưng đã xác nhận tồn tại thật qua RLOS - Metadata.xlsx</t>
+          <t>Mã người/hệ thống tạo bản ghi workflow — cột thô, dùng để loại 5 tài khoản hệ thống/test khi tính WORKSTEP_FLAG tại PDTD_DTM. Bê nguyên giá trị thô từ nguồn — không áp điều kiện CREATEDBY NOT IN ('10000380','10000020','10000420','10000140','10000100') tại SB_DWH (business rule filter chứ không phải điều kiện khóa join); PDTD_DTM tự áp điều kiện NOT IN khi tính WORKSTEP_FLAG. Cùng JOIN với WF_PROCESSNAME/WF_ACTIVITYNAME, không JOIN thêm lần nữa.</t>
         </is>
       </c>
       <c r="E35" s="31" t="inlineStr">
         <is>
-          <t>COALESCE(CASE WHEN A.WORKSTEP = 'UnderwriterMaker' THEN H.USER_MAKE END, I.UWMAKERUSER)</t>
+          <t>E.CREATEDBY</t>
         </is>
       </c>
     </row>
     <row r="36" ht="75" customHeight="1">
       <c r="A36" s="28" t="inlineStr">
         <is>
+          <t>UNDERWRITERMAKER_USERMAKE</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>User Maker CVTĐ</t>
+        </is>
+      </c>
+      <c r="D36" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI. Chỉ có giá trị khác NULL trên dòng event WORKSTEP_CODE='UnderwriterMaker'. JOIN điều kiện WORK_STEP = WORKSTEP_CODE của chính dòng event (không chỉ WI_NAME) để không fan-out. Bảng nguồn không có trong DS_BANG_202608.xlsx nhưng đã xác nhận tồn tại thật qua RLOS - Metadata.xlsx</t>
+        </is>
+      </c>
+      <c r="E36" s="31" t="inlineStr">
+        <is>
+          <t>COALESCE(CASE WHEN A.WORKSTEP = 'UnderwriterMaker' THEN F.USER_MAKE END, G.UWMAKERUSER)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
           <t>UNDERWRITERCHECKER_USERMAKE</t>
         </is>
       </c>
-      <c r="B36" s="25" t="inlineStr">
+      <c r="B37" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
-        <is>
-          <t>Người thẩm định (Checker)</t>
-        </is>
-      </c>
-      <c r="D36" s="54" t="inlineStr">
-        <is>
-          <t>CỘT MỚI: chuyển từ FCT_RLOS_APPLICATION, cùng cơ chế cột trên. Chỉ có giá trị khác NULL trên dòng event WORKSTEP_CODE='UnderwriterChecker'. Cùng JOIN duy nhất tới NG_SB_RLOS_USER_MAKE_WORK_STEP, phân biệt bằng CASE WHEN theo WORKSTEP hiện tại của dòng</t>
-        </is>
-      </c>
-      <c r="E36" s="31" t="inlineStr">
-        <is>
-          <t>COALESCE(CASE WHEN A.WORKSTEP = 'UnderwriterChecker' THEN H.USER_MAKE END, I.UWCHKRUSER)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="105" customHeight="1">
-      <c r="A37" s="28" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>User Checker CVTĐ</t>
+        </is>
+      </c>
+      <c r="D37" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI. Chỉ có giá trị khác NULL trên dòng event WORKSTEP_CODE='UnderwriterChecker'. JOIN điều kiện WORK_STEP = WORKSTEP_CODE của chính dòng event để không fan-out, cùng cơ chế cột trên.</t>
+        </is>
+      </c>
+      <c r="E37" s="31" t="inlineStr">
+        <is>
+          <t>COALESCE(CASE WHEN A.WORKSTEP = 'UnderwriterChecker' THEN F.USER_MAKE END, G.UWCHKRUSER)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="120" customHeight="1">
+      <c r="A38" s="28" t="inlineStr">
         <is>
           <t>APPROVAL_USERMAKE</t>
         </is>
       </c>
-      <c r="B37" s="25" t="inlineStr">
+      <c r="B38" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>Người phê duyệt</t>
-        </is>
-      </c>
-      <c r="D37" s="54" t="inlineStr">
-        <is>
-          <t>CỘT MỚI: chuyển từ FCT_RLOS_APPLICATION. Chỉ có giá trị khác NULL trên dòng event WORKSTEP_CODE='CreditCommittee' hoặc 'CreditApproval'. Khác hẳn công thức CLOS (không hardcode theo APP_GRP, dùng 2 cột fallback CREDAPPRUSER/CCOMMITUSER trên chính NG_SB_RLOS_EXTTABLE). Cùng JOIN duy nhất tới NG_SB_RLOS_USER_MAKE_WORK_STEP với 2 cột USERMAKE trên, phân biệt bằng CASE WHEN theo WORKSTEP hiện tại của dòng</t>
-        </is>
-      </c>
-      <c r="E37" s="31" t="inlineStr">
-        <is>
-          <t>COALESCE(CASE WHEN A.WORKSTEP IN ('CreditCommittee','CreditApproval') THEN H.USER_MAKE END, I.CREDAPPRUSER, I.CCOMMITUSER)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="10" t="n"/>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="55" t="inlineStr">
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>User Maker phê duyệt</t>
+        </is>
+      </c>
+      <c r="D38" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI. Chỉ có giá trị khác NULL trên dòng event WORKSTEP_CODE='CreditCommittee' hoặc 'CreditApproval' — khác bản cũ trên FCT_RLOS_APPLICATION vốn JOIN chỉ theo WI_NAME (không lọc WORK_STEP ở điều kiện JOIN, có nguy cơ fan-out); nay JOIN thêm điều kiện WORK_STEP=WORKSTEP_CODE nên CASE WHEN rút gọn còn đúng dòng event đang xét. Khác hẳn công thức CLOS (không hardcode theo APP_GRP, dùng 2 cột fallback CREDAPPRUSER/CCOMMITUSER trên chính G).</t>
+        </is>
+      </c>
+      <c r="E38" s="31" t="inlineStr">
+        <is>
+          <t>COALESCE(CASE WHEN F.WORK_STEP = A.WORKSTEP THEN F.USER_MAKE END, G.CREDAPPRUSER, G.CCOMMITUSER)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="10" t="n"/>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="55" t="inlineStr">
         <is>
           <t>Điều kiện join giữa các bảng</t>
         </is>
       </c>
-      <c r="E39" s="10" t="n"/>
-    </row>
-    <row r="40" ht="45" customHeight="1">
-      <c r="A40" s="25" t="n"/>
-      <c r="B40" s="25" t="n"/>
-      <c r="C40" s="51" t="n"/>
-      <c r="D40" s="54" t="n"/>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN B.WORKSTEP_CODE = A.WORKSTEP AND B.DECISION_CODE = A.DECISION AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
+      <c r="E40" s="10" t="n"/>
+    </row>
+    <row r="41" ht="45" customHeight="1">
       <c r="A41" s="25" t="n"/>
       <c r="B41" s="25" t="n"/>
       <c r="C41" s="51" t="n"/>
       <c r="D41" s="54" t="n"/>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN C.USERNAME = A.USERNAME AND v_batch_date BETWEEN C.EFF_DATE AND NVL(C.EXP_DATE, v_batch_date)</t>
+          <t>LEFT JOIN B.WORKSTEP_CODE = A.WORKSTEP AND B.DECISION_CODE = A.DECISION AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1511,7 @@
       <c r="D42" s="54" t="n"/>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN D.WI_NAME = A.WINAME AND v_batch_date BETWEEN D.EFF_DATE AND NVL(D.EXP_DATE, v_batch_date)</t>
+          <t>LEFT JOIN C.WI_NAME = A.WINAME AND v_batch_date BETWEEN C.EFF_DATE AND NVL(C.EXP_DATE, v_batch_date)</t>
         </is>
       </c>
     </row>
@@ -1506,18 +1522,18 @@
       <c r="D43" s="54" t="n"/>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN G.PROCESSINSTANCEID = A.WINAME AND ROW_NUMBER() OVER (PARTITION BY G.PROCESSINSTANCEID ORDER BY G.CREATEDBY) = 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1">
+          <t>LEFT JOIN D.USERNAME = A.USERNAME AND v_batch_date BETWEEN D.EFF_DATE AND NVL(D.EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
       <c r="A44" s="25" t="n"/>
       <c r="B44" s="25" t="n"/>
       <c r="C44" s="51" t="n"/>
       <c r="D44" s="54" t="n"/>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN H.WI_NAME = A.WINAME AND H.WORK_STEP = A.WORKSTEP</t>
+          <t>LEFT JOIN E.PROCESSINSTANCEID = A.WINAME AND ROW_NUMBER() OVER (PARTITION BY E.PROCESSINSTANCEID ORDER BY CREATEDBY) = 1</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1544,18 @@
       <c r="D45" s="54" t="n"/>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN I.WI_NAME = A.WINAME</t>
+          <t>LEFT JOIN F.WI_NAME = A.WINAME AND F.WORK_STEP = A.WORKSTEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="25" t="n"/>
+      <c r="B46" s="25" t="n"/>
+      <c r="C46" s="51" t="n"/>
+      <c r="D46" s="54" t="n"/>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN G.WI_NAME = A.WINAME</t>
         </is>
       </c>
     </row>
